--- a/examples/business-trip/traditional-design/テーブル定義書.xlsx
+++ b/examples/business-trip/traditional-design/テーブル定義書.xlsx
@@ -6837,7 +6837,7 @@
       <c r="AD17" s="80" t="n"/>
       <c r="AE17" s="148" t="inlineStr">
         <is>
-          <t>申請状態(00:下書き / 10:申請済 / 20:事前承認待ち / 21:事前承認不要 / 30:事前承認済 / 31:事前承認却下 / 40:実績登録済 / 50:最終承認済)。コードC0030001を参照する。画面遷移・登録処理で本カラムを更新する。</t>
+          <t>申請状態(00:下書き / 10:申請済 / 20:事前承認待ち / 21:事前承認不要 / 30:事前承認済 / 31:事前承認却下 / 40:実績登録済 / 50:最終承認済 / 60:経理連携済 / 90:取消済)。コードC0030001を参照する。画面遷移・登録処理で本カラムを更新する。</t>
         </is>
       </c>
       <c r="AF17" s="192" t="n"/>
